--- a/问题四/output/问题4-3_指定日期结果.xlsx
+++ b/问题四/output/问题4-3_指定日期结果.xlsx
@@ -529,40 +529,40 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>67411.18084629629</v>
+        <v>67383.60064958848</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21786.41343621399</v>
+        <v>22401.47738333333</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>17646.99488333333</v>
+        <v>18145.1966805</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>3013.450281893004</v>
+        <v>2869.685866666668</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>42154.38856131802</v>
+        <v>42670.25628643068</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>13755.72434346286</v>
+        <v>13424.23652109167</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>57991.41227085391</v>
+        <v>58267.76122776201</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>69188.25712098765</v>
+        <v>69391.51544683333</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>1777.076274691353</v>
+        <v>2007.914797244855</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1777.076274691353</v>
+        <v>2007.914797244849</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>2081.299366073018</v>
+        <v>2173.268420239649</v>
       </c>
     </row>
     <row r="3">
@@ -576,34 +576,34 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>34290.87456481481</v>
+        <v>33899.99171666666</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>18057.27814814814</v>
+        <v>16000</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>14626.3953</v>
+        <v>12960</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1081.070016666666</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>16722.944261345</v>
+        <v>17177.12875472167</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2789.078492749998</v>
+        <v>2789.078492749999</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>19737.4122983475</v>
+        <v>20191.59679172417</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>34899.27216481481</v>
+        <v>34508.38931666667</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>608.3976000000039</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>608.3975999999991</v>
+        <v>608.3975999999989</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>0</v>
@@ -623,28 +623,28 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>68276.87073971193</v>
+        <v>68149.93810955968</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>21696.65273230453</v>
+        <v>21015.37390781893</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>17574.28871316667</v>
+        <v>17022.45286533333</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>3210.142636833331</v>
+        <v>3215.938223666667</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>45066.60311337298</v>
+        <v>45829.03840584878</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>14034.19677402216</v>
+        <v>14043.75023255267</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>59100.79988739513</v>
+        <v>59872.78863840146</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>68276.87073971193</v>
+        <v>68149.93810955968</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0</v>
@@ -670,40 +670,40 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93776.07118950615</v>
+        <v>93776.07118950617</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>25612.75521666666</v>
+        <v>25645.24005925925</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>20746.3317255</v>
+        <v>20772.644448</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2467.360283333334</v>
+        <v>2465.557035333338</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>69470.19003858931</v>
+        <v>69651.21009790586</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>14628.56554398334</v>
+        <v>14619.56102509535</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>85107.66413952866</v>
+        <v>85325.66943503436</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>94550.43078333333</v>
+        <v>94583.89830925924</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>774.3595938271756</v>
+        <v>807.8271197530703</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>774.3595938271611</v>
+        <v>807.8271197530861</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>0</v>
+        <v>3.154809746774845e-12</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>1008.908556956019</v>
+        <v>1054.898312033149</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题4-3_指定日期结果.xlsx
+++ b/问题四/output/问题4-3_指定日期结果.xlsx
@@ -529,40 +529,40 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>67383.60064958848</v>
+        <v>72641.2507989537</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>22401.47738333333</v>
+        <v>21430.6926362788</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>18145.1966805</v>
+        <v>17556.36337908333</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>2869.685866666668</v>
+        <v>394.5027942500062</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>42670.25628643068</v>
+        <v>45502.02984903254</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>13424.23652109167</v>
+        <v>2044.2512129597</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>58267.76122776201</v>
+        <v>47554.21084528161</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>69391.51544683333</v>
+        <v>72648.80189478703</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>2007.914797244855</v>
+        <v>7.551095833332511</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>2007.914797244849</v>
+        <v>7.551095833333306</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>2173.268420239649</v>
+        <v>7.929783289374972</v>
       </c>
     </row>
     <row r="3">
@@ -576,40 +576,40 @@
         <v>62073.3244</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>33899.99171666666</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>16000</v>
+        <v>17098.23680860288</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>12960</v>
+        <v>13376.85565825249</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>1081.070016666666</v>
+        <v>5.684341886080801e-14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>17177.12875472167</v>
+        <v>19233.91543714997</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>2789.078492749999</v>
+        <v>1.184901066153543e-13</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>20191.59679172417</v>
+        <v>19233.91543714997</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>34508.38931666667</v>
+        <v>36037.35884483084</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>608.3976000000039</v>
+        <v>0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>608.3975999999989</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O3" s="1" t="n">
-        <v>225.3895442524993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -623,28 +623,28 @@
         <v>59065.66575</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>68149.93810955968</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>21015.37390781893</v>
+        <v>18145.78788101851</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>17022.45286533333</v>
+        <v>16321.60975502778</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>3215.938223666667</v>
+        <v>6.375000000000114</v>
       </c>
       <c r="H4" s="1" t="n">
-        <v>45829.03840584878</v>
+        <v>46262.0857404733</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>14043.75023255267</v>
+        <v>44.07993750000047</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>59872.78863840146</v>
+        <v>46306.16567797329</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>68149.93810955968</v>
+        <v>68276.81518487277</v>
       </c>
       <c r="L4" s="1" t="n">
         <v>0</v>
@@ -670,40 +670,40 @@
         <v>35338.6591</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>93776.07118950617</v>
+        <v>92381.8599591614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>25645.24005925925</v>
+        <v>21743.32376385856</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>20772.644448</v>
+        <v>18173.53895547544</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>2465.557035333338</v>
+        <v>2.273736754432321e-13</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>69651.21009790586</v>
+        <v>71442.05708125833</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>14619.56102509535</v>
+        <v>1.13755049824249e-12</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>85325.66943503436</v>
+        <v>72413.89904571924</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>94583.89830925924</v>
+        <v>92822.6187254613</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>807.8271197530703</v>
+        <v>440.7587662998994</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>807.8271197530861</v>
+        <v>440.758766299895</v>
       </c>
       <c r="N5" s="1" t="n">
-        <v>3.154809746774845e-12</v>
+        <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>1054.898312033149</v>
+        <v>971.8419644609151</v>
       </c>
     </row>
   </sheetData>

--- a/问题四/output/问题4-3_指定日期结果.xlsx
+++ b/问题四/output/问题4-3_指定日期结果.xlsx
@@ -529,40 +529,40 @@
         <v>55439.41991666666</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>72641.2507989537</v>
+        <v>72545.07421109361</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>21430.6926362788</v>
+        <v>21334.51604841872</v>
       </c>
       <c r="F2" s="1" t="n">
         <v>17556.36337908333</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>394.5027942500062</v>
+        <v>402.0538900833399</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>45502.02984903254</v>
+        <v>45460.71238688785</v>
       </c>
       <c r="I2" s="1" t="n">
-        <v>2044.2512129597</v>
+        <v>2084.543860326368</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>47554.21084528161</v>
+        <v>47545.25624721422</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>72648.80189478703</v>
+        <v>72545.07421109361</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7.551095833332511</v>
+        <v>0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>7.551095833333306</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O2" s="1" t="n">
-        <v>7.929783289374972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -673,10 +673,10 @@
         <v>92381.8599591614</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>21743.32376385856</v>
+        <v>22543.91782550566</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>18173.53895547544</v>
+        <v>18433.29574045126</v>
       </c>
       <c r="G5" s="1" t="n">
         <v>2.273736754432321e-13</v>
@@ -688,22 +688,22 @@
         <v>1.13755049824249e-12</v>
       </c>
       <c r="J5" s="1" t="n">
-        <v>72413.89904571924</v>
+        <v>73698.54685448857</v>
       </c>
       <c r="K5" s="1" t="n">
-        <v>92822.6187254613</v>
+        <v>94277.82924709134</v>
       </c>
       <c r="L5" s="1" t="n">
-        <v>440.7587662998994</v>
+        <v>1895.96928792994</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>440.758766299895</v>
+        <v>1895.969287929932</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="O5" s="1" t="n">
-        <v>971.8419644609151</v>
+        <v>2256.489773230232</v>
       </c>
     </row>
   </sheetData>
